--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20242025.xlsx
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
         <v>9</v>
@@ -938,10 +938,10 @@
         <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA2" t="n">
         <v>9</v>
@@ -1147,19 +1147,19 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX3" t="n">
         <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
         <v>5</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
         <v>5</v>
@@ -1374,10 +1374,10 @@
         <v>8</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
         <v>7</v>
@@ -1592,10 +1592,10 @@
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
         <v>10</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
         <v>5</v>
@@ -1810,10 +1810,10 @@
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
         <v>4</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV7" t="n">
         <v>4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5</v>
       </c>
       <c r="AW7" t="n">
         <v>5</v>
@@ -2028,10 +2028,10 @@
         <v>5</v>
       </c>
       <c r="AY7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>10</v>
       </c>
       <c r="BA7" t="n">
         <v>8</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
         <v>4</v>
@@ -2246,10 +2246,10 @@
         <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>6</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2464,10 +2464,10 @@
         <v>7</v>
       </c>
       <c r="AY9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
         <v>3</v>
@@ -2682,10 +2682,10 @@
         <v>2</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA10" t="n">
         <v>9</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW11" t="n">
         <v>5</v>
@@ -2900,10 +2900,10 @@
         <v>1</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA11" t="n">
         <v>4</v>
@@ -3097,19 +3097,19 @@
         <v>0.68</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW12" t="n">
         <v>2</v>
@@ -3118,10 +3118,10 @@
         <v>5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA12" t="n">
         <v>3</v>
@@ -3318,16 +3318,16 @@
         <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AU13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW13" t="n">
         <v>2</v>
@@ -3336,10 +3336,10 @@
         <v>6</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -3542,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
         <v>14</v>
@@ -3554,10 +3554,10 @@
         <v>3</v>
       </c>
       <c r="AY14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -3751,19 +3751,19 @@
         <v>1.68</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AU15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW15" t="n">
         <v>6</v>
@@ -3772,10 +3772,10 @@
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
@@ -3969,19 +3969,19 @@
         <v>1.53</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>5</v>
@@ -3990,10 +3990,10 @@
         <v>3</v>
       </c>
       <c r="AY16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
         <v>7</v>
@@ -4187,19 +4187,19 @@
         <v>0.63</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW17" t="n">
         <v>3</v>
@@ -4208,10 +4208,10 @@
         <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>3</v>
@@ -4405,19 +4405,19 @@
         <v>0.95</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
         <v>8</v>
@@ -4426,10 +4426,10 @@
         <v>1</v>
       </c>
       <c r="AY18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
         <v>8</v>
@@ -4623,19 +4623,19 @@
         <v>1.26</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="AU19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
         <v>11</v>
@@ -4644,10 +4644,10 @@
         <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
         <v>4</v>
@@ -4841,19 +4841,19 @@
         <v>0.68</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="AU20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW20" t="n">
         <v>5</v>
@@ -4862,10 +4862,10 @@
         <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA20" t="n">
         <v>8</v>
@@ -5059,19 +5059,19 @@
         <v>0.68</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW21" t="n">
         <v>7</v>
@@ -5080,10 +5080,10 @@
         <v>3</v>
       </c>
       <c r="AY21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA21" t="n">
         <v>5</v>
@@ -5277,19 +5277,19 @@
         <v>0.95</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="AU22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW22" t="n">
         <v>11</v>
@@ -5298,10 +5298,10 @@
         <v>5</v>
       </c>
       <c r="AY22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA22" t="n">
         <v>4</v>
@@ -5495,19 +5495,19 @@
         <v>0.84</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.03</v>
+        <v>2.76</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW23" t="n">
         <v>2</v>
@@ -5516,10 +5516,10 @@
         <v>5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>6</v>
@@ -5713,19 +5713,19 @@
         <v>1.05</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW24" t="n">
         <v>8</v>
@@ -5734,10 +5734,10 @@
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>7</v>
@@ -5931,19 +5931,19 @@
         <v>1.68</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="AU25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
@@ -5952,10 +5952,10 @@
         <v>6</v>
       </c>
       <c r="AY25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
         <v>11</v>
@@ -6149,19 +6149,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>3.42</v>
+        <v>3.29</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.3</v>
+        <v>4.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW26" t="n">
         <v>7</v>
@@ -6170,10 +6170,10 @@
         <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA26" t="n">
         <v>6</v>
@@ -6367,19 +6367,19 @@
         <v>0.68</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW27" t="n">
         <v>6</v>
@@ -6388,10 +6388,10 @@
         <v>4</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA27" t="n">
         <v>5</v>
@@ -6585,19 +6585,19 @@
         <v>0.63</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AU28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>2</v>
@@ -6606,10 +6606,10 @@
         <v>5</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA28" t="n">
         <v>3</v>
@@ -6803,19 +6803,19 @@
         <v>0.68</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.49</v>
+        <v>3.23</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
         <v>8</v>
@@ -6824,10 +6824,10 @@
         <v>1</v>
       </c>
       <c r="AY29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
@@ -7021,19 +7021,19 @@
         <v>1.68</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="AU30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW30" t="n">
         <v>4</v>
@@ -7042,10 +7042,10 @@
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA30" t="n">
         <v>3</v>
@@ -7239,19 +7239,19 @@
         <v>0.84</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW31" t="n">
         <v>3</v>
@@ -7260,10 +7260,10 @@
         <v>4</v>
       </c>
       <c r="AY31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>8</v>
       </c>
       <c r="BA31" t="n">
         <v>3</v>
@@ -7457,19 +7457,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="AU32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW32" t="n">
         <v>3</v>
@@ -7478,10 +7478,10 @@
         <v>6</v>
       </c>
       <c r="AY32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
         <v>1</v>
@@ -7675,19 +7675,19 @@
         <v>1.53</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="AU33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW33" t="n">
         <v>7</v>
@@ -7696,10 +7696,10 @@
         <v>10</v>
       </c>
       <c r="AY33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA33" t="n">
         <v>5</v>
@@ -7893,19 +7893,19 @@
         <v>0.95</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="AU34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW34" t="n">
         <v>2</v>
@@ -7914,10 +7914,10 @@
         <v>5</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA34" t="n">
         <v>7</v>
@@ -8111,19 +8111,19 @@
         <v>1.05</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.86</v>
+        <v>3.59</v>
       </c>
       <c r="AU35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW35" t="n">
         <v>4</v>
@@ -8132,10 +8132,10 @@
         <v>4</v>
       </c>
       <c r="AY35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA35" t="n">
         <v>3</v>
@@ -8329,19 +8329,19 @@
         <v>1.16</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="AU36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW36" t="n">
         <v>6</v>
@@ -8350,10 +8350,10 @@
         <v>4</v>
       </c>
       <c r="AY36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>12</v>
       </c>
       <c r="BA36" t="n">
         <v>6</v>
@@ -8547,19 +8547,19 @@
         <v>1.05</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW37" t="n">
         <v>6</v>
@@ -8568,10 +8568,10 @@
         <v>4</v>
       </c>
       <c r="AY37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA37" t="n">
         <v>5</v>
@@ -8765,19 +8765,19 @@
         <v>1.53</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW38" t="n">
         <v>7</v>
@@ -8786,10 +8786,10 @@
         <v>6</v>
       </c>
       <c r="AY38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA38" t="n">
         <v>9</v>
@@ -8983,19 +8983,19 @@
         <v>1.26</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AT39" t="n">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="AU39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW39" t="n">
         <v>2</v>
@@ -9004,10 +9004,10 @@
         <v>4</v>
       </c>
       <c r="AY39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA39" t="n">
         <v>4</v>
@@ -9201,19 +9201,19 @@
         <v>0.68</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="AU40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
         <v>11</v>
@@ -9222,10 +9222,10 @@
         <v>6</v>
       </c>
       <c r="AY40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA40" t="n">
         <v>4</v>
@@ -9419,16 +9419,16 @@
         <v>1.16</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV41" t="n">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         <v>4</v>
       </c>
       <c r="AX41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA41" t="n">
         <v>1</v>
@@ -9637,19 +9637,19 @@
         <v>0.95</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="AU42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW42" t="n">
         <v>5</v>
@@ -9658,10 +9658,10 @@
         <v>6</v>
       </c>
       <c r="AY42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA42" t="n">
         <v>4</v>
@@ -9855,19 +9855,19 @@
         <v>1.26</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="AU43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW43" t="n">
         <v>3</v>
@@ -9876,10 +9876,10 @@
         <v>2</v>
       </c>
       <c r="AY43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA43" t="n">
         <v>3</v>
@@ -10073,19 +10073,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="AU44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW44" t="n">
         <v>6</v>
@@ -10094,10 +10094,10 @@
         <v>5</v>
       </c>
       <c r="AY44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA44" t="n">
         <v>5</v>
@@ -10291,19 +10291,19 @@
         <v>0.95</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="AU45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW45" t="n">
         <v>1</v>
@@ -10312,10 +10312,10 @@
         <v>5</v>
       </c>
       <c r="AY45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA45" t="n">
         <v>2</v>
@@ -10509,19 +10509,19 @@
         <v>0.84</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="AU46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW46" t="n">
         <v>11</v>
@@ -10530,10 +10530,10 @@
         <v>4</v>
       </c>
       <c r="AY46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA46" t="n">
         <v>6</v>
@@ -10727,19 +10727,19 @@
         <v>0.63</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT47" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="AU47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW47" t="n">
         <v>3</v>
@@ -10748,10 +10748,10 @@
         <v>9</v>
       </c>
       <c r="AY47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA47" t="n">
         <v>4</v>
@@ -10945,19 +10945,19 @@
         <v>0.68</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="AU48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW48" t="n">
         <v>8</v>
@@ -10966,10 +10966,10 @@
         <v>4</v>
       </c>
       <c r="AY48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA48" t="n">
         <v>5</v>
@@ -11163,19 +11163,19 @@
         <v>1.68</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AU49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW49" t="n">
         <v>10</v>
@@ -11184,10 +11184,10 @@
         <v>10</v>
       </c>
       <c r="AY49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA49" t="n">
         <v>14</v>
@@ -11381,19 +11381,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="AU50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW50" t="n">
         <v>3</v>
@@ -11402,10 +11402,10 @@
         <v>6</v>
       </c>
       <c r="AY50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA50" t="n">
         <v>6</v>
@@ -11599,19 +11599,19 @@
         <v>0.68</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AU51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW51" t="n">
         <v>9</v>
@@ -11620,10 +11620,10 @@
         <v>1</v>
       </c>
       <c r="AY51" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA51" t="n">
         <v>15</v>
@@ -11817,19 +11817,19 @@
         <v>0.84</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.49</v>
+        <v>2.22</v>
       </c>
       <c r="AU52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW52" t="n">
         <v>3</v>
@@ -11838,10 +11838,10 @@
         <v>10</v>
       </c>
       <c r="AY52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA52" t="n">
         <v>4</v>
@@ -12035,19 +12035,19 @@
         <v>1.16</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="AU53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW53" t="n">
         <v>5</v>
@@ -12056,10 +12056,10 @@
         <v>3</v>
       </c>
       <c r="AY53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA53" t="n">
         <v>6</v>
@@ -12253,19 +12253,19 @@
         <v>0.95</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.66</v>
+        <v>3.39</v>
       </c>
       <c r="AU54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW54" t="n">
         <v>6</v>
@@ -12274,10 +12274,10 @@
         <v>4</v>
       </c>
       <c r="AY54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA54" t="n">
         <v>10</v>
@@ -12471,19 +12471,19 @@
         <v>1.53</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AU55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW55" t="n">
         <v>7</v>
@@ -12492,10 +12492,10 @@
         <v>5</v>
       </c>
       <c r="AY55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA55" t="n">
         <v>6</v>
@@ -12689,19 +12689,19 @@
         <v>1.26</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AU56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW56" t="n">
         <v>7</v>
@@ -12710,10 +12710,10 @@
         <v>4</v>
       </c>
       <c r="AY56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA56" t="n">
         <v>4</v>
@@ -12907,19 +12907,19 @@
         <v>1.05</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="AU57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW57" t="n">
         <v>7</v>
@@ -12928,10 +12928,10 @@
         <v>9</v>
       </c>
       <c r="AY57" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ57" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>14</v>
       </c>
       <c r="BA57" t="n">
         <v>7</v>
@@ -13125,19 +13125,19 @@
         <v>0.63</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AU58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW58" t="n">
         <v>3</v>
@@ -13146,10 +13146,10 @@
         <v>4</v>
       </c>
       <c r="AY58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA58" t="n">
         <v>2</v>
@@ -13343,19 +13343,19 @@
         <v>0.68</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AU59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW59" t="n">
         <v>11</v>
@@ -13364,10 +13364,10 @@
         <v>2</v>
       </c>
       <c r="AY59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA59" t="n">
         <v>7</v>
@@ -13561,19 +13561,19 @@
         <v>1.16</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AT60" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="AU60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW60" t="n">
         <v>1</v>
@@ -13582,10 +13582,10 @@
         <v>11</v>
       </c>
       <c r="AY60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA60" t="n">
         <v>5</v>
@@ -13779,19 +13779,19 @@
         <v>0.95</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT61" t="n">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="AU61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW61" t="n">
         <v>7</v>
@@ -13800,10 +13800,10 @@
         <v>5</v>
       </c>
       <c r="AY61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA61" t="n">
         <v>4</v>
@@ -13997,19 +13997,19 @@
         <v>0.84</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AU62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW62" t="n">
         <v>4</v>
@@ -14018,10 +14018,10 @@
         <v>6</v>
       </c>
       <c r="AY62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA62" t="n">
         <v>5</v>
@@ -14215,19 +14215,19 @@
         <v>1.68</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.77</v>
+        <v>2.51</v>
       </c>
       <c r="AU63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW63" t="n">
         <v>6</v>
@@ -14236,10 +14236,10 @@
         <v>7</v>
       </c>
       <c r="AY63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ63" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA63" t="n">
         <v>6</v>
@@ -14433,19 +14433,19 @@
         <v>0.68</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AT64" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW64" t="n">
         <v>8</v>
@@ -14454,10 +14454,10 @@
         <v>3</v>
       </c>
       <c r="AY64" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA64" t="n">
         <v>15</v>
@@ -14651,19 +14651,19 @@
         <v>0.95</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW65" t="n">
         <v>9</v>
@@ -14672,10 +14672,10 @@
         <v>4</v>
       </c>
       <c r="AY65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA65" t="n">
         <v>1</v>
@@ -14869,19 +14869,19 @@
         <v>0.95</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AT66" t="n">
-        <v>3.59</v>
+        <v>3.33</v>
       </c>
       <c r="AU66" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV66" t="n">
         <v>4</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>5</v>
       </c>
       <c r="AW66" t="n">
         <v>3</v>
@@ -14890,10 +14890,10 @@
         <v>6</v>
       </c>
       <c r="AY66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA66" t="n">
         <v>1</v>
@@ -15087,19 +15087,19 @@
         <v>1.53</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW67" t="n">
         <v>6</v>
@@ -15108,10 +15108,10 @@
         <v>5</v>
       </c>
       <c r="AY67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ67" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA67" t="n">
         <v>6</v>
@@ -15305,19 +15305,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="AU68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW68" t="n">
         <v>6</v>
@@ -15326,10 +15326,10 @@
         <v>5</v>
       </c>
       <c r="AY68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ68" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA68" t="n">
         <v>1</v>
@@ -15523,19 +15523,19 @@
         <v>1.68</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AT69" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="AU69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW69" t="n">
         <v>9</v>
@@ -15544,10 +15544,10 @@
         <v>6</v>
       </c>
       <c r="AY69" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ69" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA69" t="n">
         <v>9</v>
@@ -15741,19 +15741,19 @@
         <v>1.26</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT70" t="n">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="AU70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW70" t="n">
         <v>3</v>
@@ -15762,10 +15762,10 @@
         <v>12</v>
       </c>
       <c r="AY70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA70" t="n">
         <v>2</v>
@@ -15959,19 +15959,19 @@
         <v>0.68</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS71" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AT71" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AU71" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV71" t="n">
         <v>7</v>
-      </c>
-      <c r="AV71" t="n">
-        <v>8</v>
       </c>
       <c r="AW71" t="n">
         <v>4</v>
@@ -15980,10 +15980,10 @@
         <v>1</v>
       </c>
       <c r="AY71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA71" t="n">
         <v>4</v>
@@ -16177,19 +16177,19 @@
         <v>1.05</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT72" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AU72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW72" t="n">
         <v>5</v>
@@ -16198,10 +16198,10 @@
         <v>3</v>
       </c>
       <c r="AY72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA72" t="n">
         <v>5</v>
@@ -16395,19 +16395,19 @@
         <v>1.16</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AT73" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AU73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW73" t="n">
         <v>4</v>
@@ -16416,10 +16416,10 @@
         <v>3</v>
       </c>
       <c r="AY73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA73" t="n">
         <v>6</v>
@@ -16613,19 +16613,19 @@
         <v>0.68</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.77</v>
+        <v>2.51</v>
       </c>
       <c r="AU74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW74" t="n">
         <v>9</v>
@@ -16634,10 +16634,10 @@
         <v>4</v>
       </c>
       <c r="AY74" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA74" t="n">
         <v>4</v>
@@ -16831,19 +16831,19 @@
         <v>0.95</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AT75" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="AU75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW75" t="n">
         <v>4</v>
@@ -16852,10 +16852,10 @@
         <v>7</v>
       </c>
       <c r="AY75" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ75" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>11</v>
       </c>
       <c r="BA75" t="n">
         <v>2</v>
@@ -17049,19 +17049,19 @@
         <v>0.63</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AT76" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="AU76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW76" t="n">
         <v>9</v>
@@ -17070,10 +17070,10 @@
         <v>5</v>
       </c>
       <c r="AY76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA76" t="n">
         <v>8</v>
@@ -17267,19 +17267,19 @@
         <v>1.53</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT77" t="n">
-        <v>3.49</v>
+        <v>3.23</v>
       </c>
       <c r="AU77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW77" t="n">
         <v>7</v>
@@ -17288,10 +17288,10 @@
         <v>4</v>
       </c>
       <c r="AY77" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA77" t="n">
         <v>2</v>
@@ -17485,19 +17485,19 @@
         <v>0.68</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT78" t="n">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="AU78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW78" t="n">
         <v>7</v>
@@ -17506,10 +17506,10 @@
         <v>6</v>
       </c>
       <c r="AY78" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA78" t="n">
         <v>2</v>
@@ -17703,19 +17703,19 @@
         <v>0.84</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT79" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AU79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW79" t="n">
         <v>1</v>
@@ -17724,10 +17724,10 @@
         <v>7</v>
       </c>
       <c r="AY79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ79" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA79" t="n">
         <v>2</v>
@@ -17921,19 +17921,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="AU80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW80" t="n">
         <v>1</v>
@@ -17942,10 +17942,10 @@
         <v>6</v>
       </c>
       <c r="AY80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA80" t="n">
         <v>5</v>
@@ -18139,19 +18139,19 @@
         <v>1.68</v>
       </c>
       <c r="AR81" t="n">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="AU81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW81" t="n">
         <v>1</v>
@@ -18160,10 +18160,10 @@
         <v>8</v>
       </c>
       <c r="AY81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ81" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA81" t="n">
         <v>1</v>
@@ -18357,19 +18357,19 @@
         <v>1.26</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT82" t="n">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW82" t="n">
         <v>9</v>
@@ -18378,10 +18378,10 @@
         <v>5</v>
       </c>
       <c r="AY82" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA82" t="n">
         <v>8</v>
@@ -18575,19 +18575,19 @@
         <v>1.05</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="AU83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW83" t="n">
         <v>7</v>
@@ -18596,10 +18596,10 @@
         <v>2</v>
       </c>
       <c r="AY83" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA83" t="n">
         <v>3</v>
@@ -18793,19 +18793,19 @@
         <v>0.95</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT84" t="n">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="AU84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW84" t="n">
         <v>4</v>
@@ -18814,10 +18814,10 @@
         <v>5</v>
       </c>
       <c r="AY84" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ84" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>11</v>
       </c>
       <c r="BA84" t="n">
         <v>4</v>
@@ -19011,19 +19011,19 @@
         <v>1.16</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AT85" t="n">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="AU85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW85" t="n">
         <v>7</v>
@@ -19032,10 +19032,10 @@
         <v>4</v>
       </c>
       <c r="AY85" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA85" t="n">
         <v>8</v>
@@ -19229,19 +19229,19 @@
         <v>0.68</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AU86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW86" t="n">
         <v>7</v>
@@ -19250,10 +19250,10 @@
         <v>2</v>
       </c>
       <c r="AY86" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA86" t="n">
         <v>10</v>
@@ -19447,19 +19447,19 @@
         <v>0.95</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AT87" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="AU87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW87" t="n">
         <v>3</v>
@@ -19468,10 +19468,10 @@
         <v>3</v>
       </c>
       <c r="AY87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA87" t="n">
         <v>8</v>
@@ -19665,13 +19665,13 @@
         <v>0.63</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU88" t="n">
         <v>-1</v>
@@ -19883,19 +19883,19 @@
         <v>1.26</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT89" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="AU89" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW89" t="n">
         <v>4</v>
@@ -19904,10 +19904,10 @@
         <v>2</v>
       </c>
       <c r="AY89" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ89" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA89" t="n">
         <v>9</v>
@@ -20101,19 +20101,19 @@
         <v>1.53</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="AU90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW90" t="n">
         <v>6</v>
@@ -20122,10 +20122,10 @@
         <v>5</v>
       </c>
       <c r="AY90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA90" t="n">
         <v>4</v>
@@ -20319,19 +20319,19 @@
         <v>0.68</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT91" t="n">
-        <v>2.85</v>
+        <v>2.58</v>
       </c>
       <c r="AU91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW91" t="n">
         <v>17</v>
@@ -20340,10 +20340,10 @@
         <v>7</v>
       </c>
       <c r="AY91" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA91" t="n">
         <v>9</v>
@@ -20537,19 +20537,19 @@
         <v>1.05</v>
       </c>
       <c r="AR92" t="n">
-        <v>0.95</v>
+        <v>0.82</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="AU92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW92" t="n">
         <v>4</v>
@@ -20558,10 +20558,10 @@
         <v>8</v>
       </c>
       <c r="AY92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ92" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA92" t="n">
         <v>3</v>
@@ -20755,19 +20755,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AT93" t="n">
-        <v>3.44</v>
+        <v>3.17</v>
       </c>
       <c r="AU93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW93" t="n">
         <v>4</v>
@@ -20776,10 +20776,10 @@
         <v>3</v>
       </c>
       <c r="AY93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA93" t="n">
         <v>7</v>
@@ -20973,19 +20973,19 @@
         <v>0.84</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV94" t="n">
         <v>3</v>
-      </c>
-      <c r="AV94" t="n">
-        <v>4</v>
       </c>
       <c r="AW94" t="n">
         <v>4</v>
@@ -20994,10 +20994,10 @@
         <v>5</v>
       </c>
       <c r="AY94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ94" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA94" t="n">
         <v>0</v>
@@ -21191,19 +21191,19 @@
         <v>0.63</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AU95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW95" t="n">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>5</v>
       </c>
       <c r="AY95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ95" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA95" t="n">
         <v>4</v>
@@ -21409,19 +21409,19 @@
         <v>1.16</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.49</v>
+        <v>3.24</v>
       </c>
       <c r="AU96" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW96" t="n">
         <v>4</v>
@@ -21430,10 +21430,10 @@
         <v>4</v>
       </c>
       <c r="AY96" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA96" t="n">
         <v>7</v>
@@ -21627,19 +21627,19 @@
         <v>0.95</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="AU97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW97" t="n">
         <v>10</v>
@@ -21648,10 +21648,10 @@
         <v>3</v>
       </c>
       <c r="AY97" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA97" t="n">
         <v>5</v>
@@ -21845,19 +21845,19 @@
         <v>0.95</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="AU98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW98" t="n">
         <v>5</v>
@@ -21866,10 +21866,10 @@
         <v>5</v>
       </c>
       <c r="AY98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA98" t="n">
         <v>4</v>
@@ -22063,19 +22063,19 @@
         <v>0.68</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AU99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW99" t="n">
         <v>5</v>
@@ -22084,10 +22084,10 @@
         <v>7</v>
       </c>
       <c r="AY99" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ99" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ99" t="n">
-        <v>12</v>
       </c>
       <c r="BA99" t="n">
         <v>5</v>
@@ -22281,19 +22281,19 @@
         <v>1.16</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AT100" t="n">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="AU100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW100" t="n">
         <v>7</v>
@@ -22302,10 +22302,10 @@
         <v>2</v>
       </c>
       <c r="AY100" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA100" t="n">
         <v>6</v>
@@ -22499,19 +22499,19 @@
         <v>1.26</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.37</v>
+        <v>3.11</v>
       </c>
       <c r="AU101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW101" t="n">
         <v>6</v>
@@ -22520,10 +22520,10 @@
         <v>5</v>
       </c>
       <c r="AY101" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA101" t="n">
         <v>6</v>
@@ -22717,19 +22717,19 @@
         <v>0.68</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT102" t="n">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="AU102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW102" t="n">
         <v>5</v>
@@ -22738,10 +22738,10 @@
         <v>5</v>
       </c>
       <c r="AY102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ102" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA102" t="n">
         <v>8</v>
@@ -22935,19 +22935,19 @@
         <v>1.68</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="AU103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW103" t="n">
         <v>6</v>
@@ -22956,10 +22956,10 @@
         <v>8</v>
       </c>
       <c r="AY103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ103" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA103" t="n">
         <v>5</v>
@@ -23153,19 +23153,19 @@
         <v>1.05</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.73</v>
+        <v>2.46</v>
       </c>
       <c r="AU104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV104" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW104" t="n">
         <v>5</v>
@@ -23174,10 +23174,10 @@
         <v>13</v>
       </c>
       <c r="AY104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ104" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA104" t="n">
         <v>7</v>
@@ -23371,19 +23371,19 @@
         <v>0.63</v>
       </c>
       <c r="AR105" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AU105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV105" t="n">
         <v>3</v>
-      </c>
-      <c r="AV105" t="n">
-        <v>4</v>
       </c>
       <c r="AW105" t="n">
         <v>10</v>
@@ -23392,10 +23392,10 @@
         <v>5</v>
       </c>
       <c r="AY105" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ105" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA105" t="n">
         <v>4</v>
@@ -23589,19 +23589,19 @@
         <v>0.84</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT106" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU106" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW106" t="n">
         <v>9</v>
@@ -23610,10 +23610,10 @@
         <v>6</v>
       </c>
       <c r="AY106" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ106" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA106" t="n">
         <v>6</v>
@@ -23807,19 +23807,19 @@
         <v>1.53</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="AU107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW107" t="n">
         <v>4</v>
@@ -23828,10 +23828,10 @@
         <v>2</v>
       </c>
       <c r="AY107" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ107" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA107" t="n">
         <v>10</v>
@@ -24025,19 +24025,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AT108" t="n">
-        <v>3.49</v>
+        <v>3.23</v>
       </c>
       <c r="AU108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW108" t="n">
         <v>8</v>
@@ -24046,10 +24046,10 @@
         <v>3</v>
       </c>
       <c r="AY108" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ108" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA108" t="n">
         <v>8</v>
@@ -24243,19 +24243,19 @@
         <v>0.95</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="AU109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW109" t="n">
         <v>4</v>
@@ -24264,10 +24264,10 @@
         <v>2</v>
       </c>
       <c r="AY109" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA109" t="n">
         <v>6</v>
@@ -24461,19 +24461,19 @@
         <v>0.84</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="AU110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW110" t="n">
         <v>19</v>
@@ -24482,10 +24482,10 @@
         <v>1</v>
       </c>
       <c r="AY110" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ110" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA110" t="n">
         <v>9</v>
@@ -24679,19 +24679,19 @@
         <v>0.68</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AT111" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AU111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW111" t="n">
         <v>17</v>
@@ -24700,10 +24700,10 @@
         <v>6</v>
       </c>
       <c r="AY111" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA111" t="n">
         <v>11</v>
@@ -24897,19 +24897,19 @@
         <v>0.95</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT112" t="n">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="AU112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW112" t="n">
         <v>20</v>
@@ -24918,10 +24918,10 @@
         <v>6</v>
       </c>
       <c r="AY112" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA112" t="n">
         <v>11</v>
@@ -25115,19 +25115,19 @@
         <v>0.68</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AU113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV113" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW113" t="n">
         <v>12</v>
@@ -25136,10 +25136,10 @@
         <v>3</v>
       </c>
       <c r="AY113" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ113" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA113" t="n">
         <v>7</v>
@@ -25333,19 +25333,19 @@
         <v>1.05</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AT114" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="AU114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW114" t="n">
         <v>13</v>
@@ -25354,10 +25354,10 @@
         <v>6</v>
       </c>
       <c r="AY114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA114" t="n">
         <v>7</v>
@@ -25551,19 +25551,19 @@
         <v>1.68</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AT115" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="AU115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW115" t="n">
         <v>14</v>
@@ -25572,10 +25572,10 @@
         <v>16</v>
       </c>
       <c r="AY115" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ115" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA115" t="n">
         <v>6</v>
@@ -25769,19 +25769,19 @@
         <v>0.95</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT116" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AU116" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW116" t="n">
         <v>4</v>
@@ -25790,10 +25790,10 @@
         <v>11</v>
       </c>
       <c r="AY116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ116" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA116" t="n">
         <v>6</v>
@@ -25987,19 +25987,19 @@
         <v>1.53</v>
       </c>
       <c r="AR117" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="AU117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV117" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW117" t="n">
         <v>9</v>
@@ -26008,10 +26008,10 @@
         <v>9</v>
       </c>
       <c r="AY117" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ117" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA117" t="n">
         <v>4</v>
@@ -26205,19 +26205,19 @@
         <v>1.16</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="AU118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW118" t="n">
         <v>4</v>
@@ -26226,10 +26226,10 @@
         <v>8</v>
       </c>
       <c r="AY118" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ118" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA118" t="n">
         <v>0</v>
@@ -26423,19 +26423,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.37</v>
+        <v>3.11</v>
       </c>
       <c r="AU119" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW119" t="n">
         <v>9</v>
@@ -26444,10 +26444,10 @@
         <v>6</v>
       </c>
       <c r="AY119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ119" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA119" t="n">
         <v>5</v>
@@ -26641,19 +26641,19 @@
         <v>0.63</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT120" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW120" t="n">
         <v>15</v>
@@ -26662,10 +26662,10 @@
         <v>11</v>
       </c>
       <c r="AY120" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ120" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA120" t="n">
         <v>10</v>
@@ -26859,19 +26859,19 @@
         <v>1.26</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.18</v>
+        <v>2.91</v>
       </c>
       <c r="AU121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW121" t="n">
         <v>7</v>
@@ -26880,10 +26880,10 @@
         <v>8</v>
       </c>
       <c r="AY121" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA121" t="n">
         <v>6</v>
@@ -27077,19 +27077,19 @@
         <v>0.95</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AT122" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="AU122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW122" t="n">
         <v>16</v>
@@ -27098,10 +27098,10 @@
         <v>4</v>
       </c>
       <c r="AY122" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ122" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA122" t="n">
         <v>7</v>
@@ -27295,19 +27295,19 @@
         <v>0.63</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AT123" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AU123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW123" t="n">
         <v>10</v>
@@ -27316,10 +27316,10 @@
         <v>6</v>
       </c>
       <c r="AY123" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA123" t="n">
         <v>3</v>
@@ -27513,19 +27513,19 @@
         <v>0.84</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT124" t="n">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="AU124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW124" t="n">
         <v>15</v>
@@ -27534,10 +27534,10 @@
         <v>6</v>
       </c>
       <c r="AY124" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ124" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA124" t="n">
         <v>13</v>
@@ -27731,19 +27731,19 @@
         <v>0.95</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT125" t="n">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="AU125" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW125" t="n">
         <v>8</v>
@@ -27752,10 +27752,10 @@
         <v>7</v>
       </c>
       <c r="AY125" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ125" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA125" t="n">
         <v>4</v>
@@ -27949,19 +27949,19 @@
         <v>0.68</v>
       </c>
       <c r="AR126" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AS126" t="n">
         <v>1.01</v>
       </c>
-      <c r="AS126" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AT126" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AU126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW126" t="n">
         <v>7</v>
@@ -27970,10 +27970,10 @@
         <v>11</v>
       </c>
       <c r="AY126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ126" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA126" t="n">
         <v>2</v>
@@ -28167,19 +28167,19 @@
         <v>1.68</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="AU127" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV127" t="n">
         <v>7</v>
-      </c>
-      <c r="AV127" t="n">
-        <v>8</v>
       </c>
       <c r="AW127" t="n">
         <v>14</v>
@@ -28188,10 +28188,10 @@
         <v>9</v>
       </c>
       <c r="AY127" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ127" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA127" t="n">
         <v>6</v>
@@ -28385,19 +28385,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR128" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS128" t="n">
         <v>1.49</v>
       </c>
-      <c r="AS128" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AT128" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU128" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV128" t="n">
         <v>7</v>
-      </c>
-      <c r="AV128" t="n">
-        <v>8</v>
       </c>
       <c r="AW128" t="n">
         <v>10</v>
@@ -28406,10 +28406,10 @@
         <v>8</v>
       </c>
       <c r="AY128" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ128" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA128" t="n">
         <v>4</v>
@@ -28603,19 +28603,19 @@
         <v>1.53</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT129" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="AU129" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV129" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW129" t="n">
         <v>8</v>
@@ -28624,10 +28624,10 @@
         <v>8</v>
       </c>
       <c r="AY129" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ129" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA129" t="n">
         <v>6</v>
@@ -28821,19 +28821,19 @@
         <v>1.16</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AT130" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="AU130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV130" t="n">
         <v>4</v>
-      </c>
-      <c r="AV130" t="n">
-        <v>5</v>
       </c>
       <c r="AW130" t="n">
         <v>16</v>
@@ -28842,10 +28842,10 @@
         <v>2</v>
       </c>
       <c r="AY130" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA130" t="n">
         <v>7</v>
@@ -29039,19 +29039,19 @@
         <v>0.68</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AT131" t="n">
-        <v>3.16</v>
+        <v>2.89</v>
       </c>
       <c r="AU131" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW131" t="n">
         <v>21</v>
@@ -29060,10 +29060,10 @@
         <v>3</v>
       </c>
       <c r="AY131" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AZ131" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA131" t="n">
         <v>8</v>
@@ -29257,19 +29257,19 @@
         <v>1.05</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AT132" t="n">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="AU132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW132" t="n">
         <v>6</v>
@@ -29278,10 +29278,10 @@
         <v>21</v>
       </c>
       <c r="AY132" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ132" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA132" t="n">
         <v>4</v>
@@ -29475,19 +29475,19 @@
         <v>1.26</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AU133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW133" t="n">
         <v>6</v>
@@ -29496,10 +29496,10 @@
         <v>14</v>
       </c>
       <c r="AY133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ133" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA133" t="n">
         <v>2</v>
@@ -29693,19 +29693,19 @@
         <v>0.68</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT134" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AU134" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW134" t="n">
         <v>10</v>
@@ -29714,10 +29714,10 @@
         <v>5</v>
       </c>
       <c r="AY134" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ134" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA134" t="n">
         <v>5</v>
@@ -29911,19 +29911,19 @@
         <v>0.84</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT135" t="n">
-        <v>3.19</v>
+        <v>2.92</v>
       </c>
       <c r="AU135" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW135" t="n">
         <v>17</v>
@@ -29932,10 +29932,10 @@
         <v>4</v>
       </c>
       <c r="AY135" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA135" t="n">
         <v>10</v>
@@ -30129,19 +30129,19 @@
         <v>0.63</v>
       </c>
       <c r="AR136" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="AU136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW136" t="n">
         <v>11</v>
@@ -30150,10 +30150,10 @@
         <v>9</v>
       </c>
       <c r="AY136" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ136" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA136" t="n">
         <v>5</v>
@@ -30347,19 +30347,19 @@
         <v>1.68</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AT137" t="n">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="AU137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW137" t="n">
         <v>10</v>
@@ -30368,10 +30368,10 @@
         <v>4</v>
       </c>
       <c r="AY137" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ137" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA137" t="n">
         <v>10</v>
@@ -30565,19 +30565,19 @@
         <v>0.68</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU138" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW138" t="n">
         <v>13</v>
@@ -30586,10 +30586,10 @@
         <v>8</v>
       </c>
       <c r="AY138" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ138" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA138" t="n">
         <v>3</v>
@@ -30783,19 +30783,19 @@
         <v>0.95</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="AU139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW139" t="n">
         <v>16</v>
@@ -30804,10 +30804,10 @@
         <v>6</v>
       </c>
       <c r="AY139" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ139" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA139" t="n">
         <v>8</v>
@@ -31001,19 +31001,19 @@
         <v>1.26</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT140" t="n">
-        <v>3.32</v>
+        <v>3.06</v>
       </c>
       <c r="AU140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW140" t="n">
         <v>2</v>
@@ -31022,10 +31022,10 @@
         <v>9</v>
       </c>
       <c r="AY140" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ140" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA140" t="n">
         <v>1</v>
@@ -31219,19 +31219,19 @@
         <v>1.05</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AT141" t="n">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="AU141" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV141" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW141" t="n">
         <v>12</v>
@@ -31240,10 +31240,10 @@
         <v>9</v>
       </c>
       <c r="AY141" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ141" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA141" t="n">
         <v>5</v>
@@ -31437,19 +31437,19 @@
         <v>0.95</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT142" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="AU142" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW142" t="n">
         <v>9</v>
@@ -31458,10 +31458,10 @@
         <v>12</v>
       </c>
       <c r="AY142" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ142" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA142" t="n">
         <v>4</v>
@@ -31655,19 +31655,19 @@
         <v>0.95</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="AU143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW143" t="n">
         <v>13</v>
@@ -31676,10 +31676,10 @@
         <v>6</v>
       </c>
       <c r="AY143" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ143" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA143" t="n">
         <v>2</v>
@@ -31873,19 +31873,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AT144" t="n">
-        <v>3.44</v>
+        <v>3.17</v>
       </c>
       <c r="AU144" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV144" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW144" t="n">
         <v>13</v>
@@ -31894,10 +31894,10 @@
         <v>9</v>
       </c>
       <c r="AY144" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ144" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA144" t="n">
         <v>9</v>
@@ -32091,19 +32091,19 @@
         <v>1.53</v>
       </c>
       <c r="AR145" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS145" t="n">
         <v>1.53</v>
       </c>
-      <c r="AS145" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AT145" t="n">
-        <v>3.19</v>
+        <v>2.93</v>
       </c>
       <c r="AU145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW145" t="n">
         <v>11</v>
@@ -32112,10 +32112,10 @@
         <v>4</v>
       </c>
       <c r="AY145" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA145" t="n">
         <v>5</v>
@@ -32309,19 +32309,19 @@
         <v>0.84</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT146" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AU146" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW146" t="n">
         <v>9</v>
@@ -32330,10 +32330,10 @@
         <v>9</v>
       </c>
       <c r="AY146" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ146" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA146" t="n">
         <v>7</v>
@@ -32527,19 +32527,19 @@
         <v>0.68</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU147" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW147" t="n">
         <v>7</v>
@@ -32548,10 +32548,10 @@
         <v>5</v>
       </c>
       <c r="AY147" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ147" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA147" t="n">
         <v>9</v>
@@ -32745,19 +32745,19 @@
         <v>1.68</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AT148" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AU148" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW148" t="n">
         <v>11</v>
@@ -32766,10 +32766,10 @@
         <v>8</v>
       </c>
       <c r="AY148" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ148" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA148" t="n">
         <v>9</v>
@@ -32963,19 +32963,19 @@
         <v>0.63</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT149" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV149" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW149" t="n">
         <v>7</v>
@@ -32984,10 +32984,10 @@
         <v>19</v>
       </c>
       <c r="AY149" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ149" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA149" t="n">
         <v>1</v>
@@ -33181,19 +33181,19 @@
         <v>0.68</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AU150" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW150" t="n">
         <v>9</v>
@@ -33202,10 +33202,10 @@
         <v>3</v>
       </c>
       <c r="AY150" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
@@ -33399,19 +33399,19 @@
         <v>1.16</v>
       </c>
       <c r="AR151" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT151" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="AU151" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV151" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW151" t="n">
         <v>8</v>
@@ -33420,10 +33420,10 @@
         <v>10</v>
       </c>
       <c r="AY151" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ151" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ151" t="n">
-        <v>14</v>
       </c>
       <c r="BA151" t="n">
         <v>3</v>
@@ -33617,19 +33617,19 @@
         <v>0.63</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT152" t="n">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="AU152" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW152" t="n">
         <v>7</v>
@@ -33638,10 +33638,10 @@
         <v>6</v>
       </c>
       <c r="AY152" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ152" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA152" t="n">
         <v>10</v>
@@ -33835,19 +33835,19 @@
         <v>0.95</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AU153" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW153" t="n">
         <v>8</v>
@@ -33856,10 +33856,10 @@
         <v>16</v>
       </c>
       <c r="AY153" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ153" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA153" t="n">
         <v>3</v>
@@ -34053,19 +34053,19 @@
         <v>1.53</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT154" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="AU154" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW154" t="n">
         <v>8</v>
@@ -34074,10 +34074,10 @@
         <v>9</v>
       </c>
       <c r="AY154" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ154" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA154" t="n">
         <v>6</v>
@@ -34271,19 +34271,19 @@
         <v>1.26</v>
       </c>
       <c r="AR155" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT155" t="n">
-        <v>3.59</v>
+        <v>3.33</v>
       </c>
       <c r="AU155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV155" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW155" t="n">
         <v>15</v>
@@ -34292,10 +34292,10 @@
         <v>8</v>
       </c>
       <c r="AY155" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ155" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA155" t="n">
         <v>7</v>
@@ -34489,19 +34489,19 @@
         <v>0.95</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="AU156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW156" t="n">
         <v>4</v>
@@ -34510,10 +34510,10 @@
         <v>14</v>
       </c>
       <c r="AY156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ156" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA156" t="n">
         <v>3</v>
@@ -34707,19 +34707,19 @@
         <v>1.05</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="AU157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW157" t="n">
         <v>8</v>
@@ -34728,10 +34728,10 @@
         <v>7</v>
       </c>
       <c r="AY157" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ157" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA157" t="n">
         <v>5</v>
@@ -34925,19 +34925,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR158" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT158" t="n">
-        <v>3.71</v>
+        <v>3.44</v>
       </c>
       <c r="AU158" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW158" t="n">
         <v>5</v>
@@ -34946,10 +34946,10 @@
         <v>7</v>
       </c>
       <c r="AY158" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ158" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA158" t="n">
         <v>1</v>
@@ -35143,19 +35143,19 @@
         <v>0.68</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AU159" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW159" t="n">
         <v>17</v>
@@ -35164,10 +35164,10 @@
         <v>7</v>
       </c>
       <c r="AY159" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA159" t="n">
         <v>6</v>
@@ -35361,19 +35361,19 @@
         <v>0.84</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT160" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU160" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW160" t="n">
         <v>10</v>
@@ -35382,10 +35382,10 @@
         <v>3</v>
       </c>
       <c r="AY160" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ160" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA160" t="n">
         <v>6</v>
@@ -35579,19 +35579,19 @@
         <v>1.53</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT161" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="AU161" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW161" t="n">
         <v>6</v>
@@ -35600,10 +35600,10 @@
         <v>4</v>
       </c>
       <c r="AY161" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ161" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA161" t="n">
         <v>9</v>
@@ -35797,19 +35797,19 @@
         <v>1.68</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AT162" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="AU162" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW162" t="n">
         <v>7</v>
@@ -35818,10 +35818,10 @@
         <v>8</v>
       </c>
       <c r="AY162" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ162" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA162" t="n">
         <v>6</v>
@@ -36015,19 +36015,19 @@
         <v>1.16</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AT163" t="n">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
       <c r="AU163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW163" t="n">
         <v>8</v>
@@ -36036,10 +36036,10 @@
         <v>15</v>
       </c>
       <c r="AY163" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ163" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA163" t="n">
         <v>4</v>
@@ -36233,19 +36233,19 @@
         <v>0.68</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AT164" t="n">
-        <v>3.19</v>
+        <v>2.92</v>
       </c>
       <c r="AU164" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW164" t="n">
         <v>8</v>
@@ -36254,10 +36254,10 @@
         <v>11</v>
       </c>
       <c r="AY164" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ164" t="n">
         <v>15</v>
-      </c>
-      <c r="AZ164" t="n">
-        <v>16</v>
       </c>
       <c r="BA164" t="n">
         <v>8</v>
@@ -36451,19 +36451,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT165" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AU165" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV165" t="n">
         <v>6</v>
-      </c>
-      <c r="AV165" t="n">
-        <v>7</v>
       </c>
       <c r="AW165" t="n">
         <v>8</v>
@@ -36472,10 +36472,10 @@
         <v>9</v>
       </c>
       <c r="AY165" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ165" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA165" t="n">
         <v>8</v>
@@ -36669,19 +36669,19 @@
         <v>1.05</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT166" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AU166" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV166" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW166" t="n">
         <v>15</v>
@@ -36690,10 +36690,10 @@
         <v>4</v>
       </c>
       <c r="AY166" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ166" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA166" t="n">
         <v>6</v>
@@ -36887,19 +36887,19 @@
         <v>0.63</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AU167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV167" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW167" t="n">
         <v>7</v>
@@ -36908,10 +36908,10 @@
         <v>8</v>
       </c>
       <c r="AY167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ167" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA167" t="n">
         <v>6</v>
@@ -37105,19 +37105,19 @@
         <v>0.95</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AT168" t="n">
-        <v>3.63</v>
+        <v>3.37</v>
       </c>
       <c r="AU168" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV168" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW168" t="n">
         <v>14</v>
@@ -37126,10 +37126,10 @@
         <v>6</v>
       </c>
       <c r="AY168" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ168" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA168" t="n">
         <v>3</v>
@@ -37323,19 +37323,19 @@
         <v>0.68</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT169" t="n">
-        <v>3.19</v>
+        <v>2.93</v>
       </c>
       <c r="AU169" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW169" t="n">
         <v>4</v>
@@ -37344,10 +37344,10 @@
         <v>1</v>
       </c>
       <c r="AY169" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA169" t="n">
         <v>9</v>
@@ -37541,19 +37541,19 @@
         <v>0.95</v>
       </c>
       <c r="AR170" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT170" t="n">
-        <v>3.49</v>
+        <v>3.23</v>
       </c>
       <c r="AU170" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW170" t="n">
         <v>6</v>
@@ -37562,10 +37562,10 @@
         <v>7</v>
       </c>
       <c r="AY170" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA170" t="n">
         <v>9</v>
@@ -37759,19 +37759,19 @@
         <v>0.68</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.91</v>
+        <v>2.64</v>
       </c>
       <c r="AU171" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV171" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW171" t="n">
         <v>10</v>
@@ -37780,10 +37780,10 @@
         <v>10</v>
       </c>
       <c r="AY171" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ171" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA171" t="n">
         <v>5</v>
@@ -37977,19 +37977,19 @@
         <v>1.53</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT172" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="AU172" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW172" t="n">
         <v>7</v>
@@ -37998,10 +37998,10 @@
         <v>7</v>
       </c>
       <c r="AY172" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ172" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA172" t="n">
         <v>9</v>
@@ -38195,19 +38195,19 @@
         <v>1.68</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT173" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AU173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV173" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW173" t="n">
         <v>4</v>
@@ -38216,10 +38216,10 @@
         <v>10</v>
       </c>
       <c r="AY173" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ173" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA173" t="n">
         <v>2</v>
@@ -38413,19 +38413,19 @@
         <v>1.26</v>
       </c>
       <c r="AR174" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS174" t="n">
         <v>1.47</v>
       </c>
-      <c r="AS174" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AT174" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AU174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV174" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW174" t="n">
         <v>7</v>
@@ -38434,10 +38434,10 @@
         <v>13</v>
       </c>
       <c r="AY174" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ174" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA174" t="n">
         <v>4</v>
@@ -38631,19 +38631,19 @@
         <v>1.05</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT175" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="AU175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV175" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW175" t="n">
         <v>8</v>
@@ -38652,10 +38652,10 @@
         <v>4</v>
       </c>
       <c r="AY175" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ175" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ175" t="n">
-        <v>13</v>
       </c>
       <c r="BA175" t="n">
         <v>6</v>
@@ -38849,19 +38849,19 @@
         <v>0.95</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AT176" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AU176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV176" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW176" t="n">
         <v>7</v>
@@ -38870,10 +38870,10 @@
         <v>5</v>
       </c>
       <c r="AY176" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ176" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA176" t="n">
         <v>3</v>
@@ -39067,19 +39067,19 @@
         <v>1.16</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="AU177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV177" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW177" t="n">
         <v>6</v>
@@ -39088,10 +39088,10 @@
         <v>5</v>
       </c>
       <c r="AY177" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ177" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA177" t="n">
         <v>3</v>
@@ -39285,19 +39285,19 @@
         <v>0.68</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT178" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU178" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW178" t="n">
         <v>9</v>
@@ -39306,10 +39306,10 @@
         <v>8</v>
       </c>
       <c r="AY178" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ178" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA178" t="n">
         <v>3</v>
@@ -39503,19 +39503,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS179" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT179" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="AU179" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV179" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW179" t="n">
         <v>11</v>
@@ -39524,10 +39524,10 @@
         <v>8</v>
       </c>
       <c r="AY179" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ179" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA179" t="n">
         <v>5</v>
@@ -39721,19 +39721,19 @@
         <v>0.84</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT180" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="AU180" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW180" t="n">
         <v>7</v>
@@ -39742,10 +39742,10 @@
         <v>9</v>
       </c>
       <c r="AY180" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ180" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA180" t="n">
         <v>5</v>
@@ -39939,19 +39939,19 @@
         <v>0.95</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT181" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AU181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV181" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW181" t="n">
         <v>11</v>
@@ -39960,10 +39960,10 @@
         <v>10</v>
       </c>
       <c r="AY181" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ181" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA181" t="n">
         <v>4</v>
@@ -40157,19 +40157,19 @@
         <v>1.26</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AU182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW182" t="n">
         <v>8</v>
@@ -40178,10 +40178,10 @@
         <v>15</v>
       </c>
       <c r="AY182" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ182" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA182" t="n">
         <v>7</v>
@@ -40375,19 +40375,19 @@
         <v>0.63</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS183" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT183" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AU183" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW183" t="n">
         <v>16</v>
@@ -40396,10 +40396,10 @@
         <v>3</v>
       </c>
       <c r="AY183" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ183" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA183" t="n">
         <v>15</v>
@@ -40593,19 +40593,19 @@
         <v>0.68</v>
       </c>
       <c r="AR184" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AT184" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AU184" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW184" t="n">
         <v>16</v>
@@ -40614,10 +40614,10 @@
         <v>11</v>
       </c>
       <c r="AY184" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ184" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA184" t="n">
         <v>9</v>
@@ -40811,19 +40811,19 @@
         <v>1.53</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS185" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT185" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="AU185" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV185" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW185" t="n">
         <v>10</v>
@@ -40832,10 +40832,10 @@
         <v>12</v>
       </c>
       <c r="AY185" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ185" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA185" t="n">
         <v>5</v>
@@ -41029,19 +41029,19 @@
         <v>1.16</v>
       </c>
       <c r="AR186" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS186" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT186" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AU186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW186" t="n">
         <v>6</v>
@@ -41050,10 +41050,10 @@
         <v>10</v>
       </c>
       <c r="AY186" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ186" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA186" t="n">
         <v>3</v>
@@ -41247,19 +41247,19 @@
         <v>1.05</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT187" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AU187" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW187" t="n">
         <v>6</v>
@@ -41268,10 +41268,10 @@
         <v>14</v>
       </c>
       <c r="AY187" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ187" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA187" t="n">
         <v>2</v>
@@ -41465,19 +41465,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR188" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS188" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AT188" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AU188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW188" t="n">
         <v>7</v>
@@ -41486,10 +41486,10 @@
         <v>18</v>
       </c>
       <c r="AY188" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ188" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA188" t="n">
         <v>4</v>
@@ -41683,19 +41683,19 @@
         <v>0.84</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS189" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT189" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="AU189" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV189" t="n">
         <v>5</v>
-      </c>
-      <c r="AV189" t="n">
-        <v>6</v>
       </c>
       <c r="AW189" t="n">
         <v>13</v>
@@ -41704,10 +41704,10 @@
         <v>4</v>
       </c>
       <c r="AY189" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ189" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA189" t="n">
         <v>3</v>
@@ -41901,19 +41901,19 @@
         <v>1.68</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS190" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AT190" t="n">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="AU190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV190" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW190" t="n">
         <v>10</v>
@@ -41922,10 +41922,10 @@
         <v>9</v>
       </c>
       <c r="AY190" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ190" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA190" t="n">
         <v>5</v>
@@ -42119,19 +42119,19 @@
         <v>0.95</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT191" t="n">
-        <v>3.43</v>
+        <v>3.17</v>
       </c>
       <c r="AU191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW191" t="n">
         <v>7</v>
@@ -42140,10 +42140,10 @@
         <v>7</v>
       </c>
       <c r="AY191" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ191" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA191" t="n">
         <v>7</v>
@@ -42337,19 +42337,19 @@
         <v>0.95</v>
       </c>
       <c r="AR192" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS192" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT192" t="n">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="AU192" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW192" t="n">
         <v>6</v>
@@ -42358,10 +42358,10 @@
         <v>12</v>
       </c>
       <c r="AY192" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ192" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA192" t="n">
         <v>5</v>
@@ -42555,19 +42555,19 @@
         <v>1.53</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS193" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT193" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="AU193" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV193" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW193" t="n">
         <v>5</v>
@@ -42576,10 +42576,10 @@
         <v>13</v>
       </c>
       <c r="AY193" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ193" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA193" t="n">
         <v>2</v>
@@ -42773,19 +42773,19 @@
         <v>0.68</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AU194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW194" t="n">
         <v>10</v>
@@ -42794,10 +42794,10 @@
         <v>12</v>
       </c>
       <c r="AY194" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ194" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA194" t="n">
         <v>4</v>
@@ -42991,19 +42991,19 @@
         <v>1.05</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS195" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT195" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="AU195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV195" t="n">
         <v>5</v>
-      </c>
-      <c r="AV195" t="n">
-        <v>6</v>
       </c>
       <c r="AW195" t="n">
         <v>5</v>
@@ -43012,10 +43012,10 @@
         <v>4</v>
       </c>
       <c r="AY195" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ195" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA195" t="n">
         <v>5</v>
@@ -43209,19 +43209,19 @@
         <v>0.63</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT196" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="AU196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW196" t="n">
         <v>9</v>
@@ -43230,10 +43230,10 @@
         <v>14</v>
       </c>
       <c r="AY196" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ196" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA196" t="n">
         <v>8</v>
@@ -43427,19 +43427,19 @@
         <v>0.68</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT197" t="n">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="AU197" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW197" t="n">
         <v>8</v>
@@ -43448,10 +43448,10 @@
         <v>10</v>
       </c>
       <c r="AY197" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ197" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA197" t="n">
         <v>2</v>
@@ -43645,19 +43645,19 @@
         <v>1.16</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS198" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT198" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="AU198" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV198" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW198" t="n">
         <v>6</v>
@@ -43666,10 +43666,10 @@
         <v>9</v>
       </c>
       <c r="AY198" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ198" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA198" t="n">
         <v>5</v>
@@ -43863,19 +43863,19 @@
         <v>1.26</v>
       </c>
       <c r="AR199" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AS199" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AT199" t="n">
-        <v>3.69</v>
+        <v>3.42</v>
       </c>
       <c r="AU199" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV199" t="n">
         <v>6</v>
-      </c>
-      <c r="AV199" t="n">
-        <v>7</v>
       </c>
       <c r="AW199" t="n">
         <v>17</v>
@@ -43884,10 +43884,10 @@
         <v>10</v>
       </c>
       <c r="AY199" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ199" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA199" t="n">
         <v>7</v>
@@ -44081,19 +44081,19 @@
         <v>0.84</v>
       </c>
       <c r="AR200" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AS200" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AT200" t="n">
-        <v>2.49</v>
+        <v>2.22</v>
       </c>
       <c r="AU200" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV200" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW200" t="n">
         <v>7</v>
@@ -44102,10 +44102,10 @@
         <v>8</v>
       </c>
       <c r="AY200" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ200" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ200" t="n">
-        <v>14</v>
       </c>
       <c r="BA200" t="n">
         <v>3</v>
@@ -44299,19 +44299,19 @@
         <v>0.95</v>
       </c>
       <c r="AR201" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AT201" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="AU201" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV201" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW201" t="n">
         <v>10</v>
@@ -44320,10 +44320,10 @@
         <v>8</v>
       </c>
       <c r="AY201" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ201" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA201" t="n">
         <v>5</v>
@@ -44517,19 +44517,19 @@
         <v>1.26</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS202" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT202" t="n">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="AU202" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV202" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW202" t="n">
         <v>2</v>
@@ -44538,10 +44538,10 @@
         <v>10</v>
       </c>
       <c r="AY202" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ202" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA202" t="n">
         <v>1</v>
@@ -44735,19 +44735,19 @@
         <v>1.53</v>
       </c>
       <c r="AR203" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT203" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="AU203" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW203" t="n">
         <v>6</v>
@@ -44756,10 +44756,10 @@
         <v>6</v>
       </c>
       <c r="AY203" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ203" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA203" t="n">
         <v>10</v>
@@ -44953,19 +44953,19 @@
         <v>1.16</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AT204" t="n">
-        <v>3.29</v>
+        <v>3.04</v>
       </c>
       <c r="AU204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV204" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW204" t="n">
         <v>18</v>
@@ -44974,10 +44974,10 @@
         <v>4</v>
       </c>
       <c r="AY204" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ204" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA204" t="n">
         <v>11</v>
@@ -45171,19 +45171,19 @@
         <v>0.95</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AU205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV205" t="n">
         <v>3</v>
-      </c>
-      <c r="AV205" t="n">
-        <v>4</v>
       </c>
       <c r="AW205" t="n">
         <v>11</v>
@@ -45192,10 +45192,10 @@
         <v>7</v>
       </c>
       <c r="AY205" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ205" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA205" t="n">
         <v>7</v>
@@ -45389,19 +45389,19 @@
         <v>0.68</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS206" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT206" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU206" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV206" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW206" t="n">
         <v>17</v>
@@ -45410,10 +45410,10 @@
         <v>8</v>
       </c>
       <c r="AY206" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ206" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA206" t="n">
         <v>7</v>
@@ -45607,19 +45607,19 @@
         <v>0.63</v>
       </c>
       <c r="AR207" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS207" t="n">
         <v>1.33</v>
       </c>
-      <c r="AS207" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AT207" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="AU207" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV207" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW207" t="n">
         <v>10</v>
@@ -45628,10 +45628,10 @@
         <v>4</v>
       </c>
       <c r="AY207" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ207" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA207" t="n">
         <v>6</v>
@@ -45825,19 +45825,19 @@
         <v>0.84</v>
       </c>
       <c r="AR208" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AS208" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT208" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AU208" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW208" t="n">
         <v>12</v>
@@ -45846,10 +45846,10 @@
         <v>6</v>
       </c>
       <c r="AY208" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ208" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA208" t="n">
         <v>5</v>
@@ -46043,19 +46043,19 @@
         <v>1.68</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS209" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AT209" t="n">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="AU209" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV209" t="n">
         <v>7</v>
-      </c>
-      <c r="AV209" t="n">
-        <v>8</v>
       </c>
       <c r="AW209" t="n">
         <v>14</v>
@@ -46064,10 +46064,10 @@
         <v>7</v>
       </c>
       <c r="AY209" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ209" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA209" t="n">
         <v>5</v>
@@ -46261,19 +46261,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT210" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AU210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV210" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW210" t="n">
         <v>4</v>
@@ -46282,10 +46282,10 @@
         <v>9</v>
       </c>
       <c r="AY210" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ210" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA210" t="n">
         <v>6</v>
@@ -46479,19 +46479,19 @@
         <v>0.95</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT211" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="AU211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV211" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW211" t="n">
         <v>12</v>
@@ -46500,10 +46500,10 @@
         <v>14</v>
       </c>
       <c r="AY211" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ211" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA211" t="n">
         <v>7</v>
@@ -46697,19 +46697,19 @@
         <v>0.68</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AU212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV212" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW212" t="n">
         <v>15</v>
@@ -46718,10 +46718,10 @@
         <v>8</v>
       </c>
       <c r="AY212" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ212" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA212" t="n">
         <v>8</v>
@@ -46915,19 +46915,19 @@
         <v>0.95</v>
       </c>
       <c r="AR213" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS213" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT213" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV213" t="n">
         <v>3</v>
-      </c>
-      <c r="AV213" t="n">
-        <v>4</v>
       </c>
       <c r="AW213" t="n">
         <v>7</v>
@@ -46936,10 +46936,10 @@
         <v>7</v>
       </c>
       <c r="AY213" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ213" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ213" t="n">
-        <v>11</v>
       </c>
       <c r="BA213" t="n">
         <v>1</v>
@@ -47133,19 +47133,19 @@
         <v>1.68</v>
       </c>
       <c r="AR214" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AS214" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AT214" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="AU214" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV214" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW214" t="n">
         <v>15</v>
@@ -47154,10 +47154,10 @@
         <v>10</v>
       </c>
       <c r="AY214" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ214" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA214" t="n">
         <v>5</v>
@@ -47351,19 +47351,19 @@
         <v>0.68</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AU215" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW215" t="n">
         <v>8</v>
@@ -47372,10 +47372,10 @@
         <v>3</v>
       </c>
       <c r="AY215" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ215" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA215" t="n">
         <v>4</v>
@@ -47569,19 +47569,19 @@
         <v>1.16</v>
       </c>
       <c r="AR216" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AS216" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT216" t="n">
-        <v>3.46</v>
+        <v>3.19</v>
       </c>
       <c r="AU216" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW216" t="n">
         <v>8</v>
@@ -47590,10 +47590,10 @@
         <v>7</v>
       </c>
       <c r="AY216" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ216" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA216" t="n">
         <v>10</v>
@@ -47787,19 +47787,19 @@
         <v>1.05</v>
       </c>
       <c r="AR217" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AS217" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT217" t="n">
-        <v>3.69</v>
+        <v>3.43</v>
       </c>
       <c r="AU217" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV217" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW217" t="n">
         <v>12</v>
@@ -47808,10 +47808,10 @@
         <v>6</v>
       </c>
       <c r="AY217" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ217" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA217" t="n">
         <v>4</v>
@@ -48005,19 +48005,19 @@
         <v>1.26</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AS218" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AT218" t="n">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="AU218" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV218" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW218" t="n">
         <v>9</v>
@@ -48026,10 +48026,10 @@
         <v>9</v>
       </c>
       <c r="AY218" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ218" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA218" t="n">
         <v>9</v>
@@ -48223,19 +48223,19 @@
         <v>0.68</v>
       </c>
       <c r="AR219" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS219" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AT219" t="n">
-        <v>2.49</v>
+        <v>2.22</v>
       </c>
       <c r="AU219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW219" t="n">
         <v>8</v>
@@ -48244,10 +48244,10 @@
         <v>4</v>
       </c>
       <c r="AY219" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ219" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA219" t="n">
         <v>9</v>
@@ -48441,19 +48441,19 @@
         <v>0.84</v>
       </c>
       <c r="AR220" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="AU220" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW220" t="n">
         <v>9</v>
@@ -48462,10 +48462,10 @@
         <v>13</v>
       </c>
       <c r="AY220" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ220" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA220" t="n">
         <v>3</v>
@@ -48659,19 +48659,19 @@
         <v>1.68</v>
       </c>
       <c r="AR221" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AS221" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AT221" t="n">
-        <v>3.92</v>
+        <v>3.66</v>
       </c>
       <c r="AU221" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV221" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW221" t="n">
         <v>6</v>
@@ -48680,10 +48680,10 @@
         <v>15</v>
       </c>
       <c r="AY221" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ221" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA221" t="n">
         <v>3</v>
@@ -48877,19 +48877,19 @@
         <v>1.16</v>
       </c>
       <c r="AR222" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS222" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT222" t="n">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AU222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW222" t="n">
         <v>10</v>
@@ -48898,10 +48898,10 @@
         <v>4</v>
       </c>
       <c r="AY222" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ222" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA222" t="n">
         <v>11</v>
@@ -49095,19 +49095,19 @@
         <v>1.53</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT223" t="n">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="AU223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV223" t="n">
         <v>7</v>
-      </c>
-      <c r="AV223" t="n">
-        <v>8</v>
       </c>
       <c r="AW223" t="n">
         <v>7</v>
@@ -49116,10 +49116,10 @@
         <v>11</v>
       </c>
       <c r="AY223" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ223" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA223" t="n">
         <v>2</v>
@@ -49313,19 +49313,19 @@
         <v>0.63</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS224" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT224" t="n">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="AU224" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW224" t="n">
         <v>6</v>
@@ -49334,10 +49334,10 @@
         <v>8</v>
       </c>
       <c r="AY224" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ224" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA224" t="n">
         <v>10</v>
@@ -49531,19 +49531,19 @@
         <v>0.95</v>
       </c>
       <c r="AR225" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW225" t="n">
         <v>18</v>
@@ -49552,10 +49552,10 @@
         <v>6</v>
       </c>
       <c r="AY225" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ225" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA225" t="n">
         <v>10</v>
@@ -49749,19 +49749,19 @@
         <v>1.26</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AS226" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AT226" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="AU226" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV226" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW226" t="n">
         <v>10</v>
@@ -49770,10 +49770,10 @@
         <v>4</v>
       </c>
       <c r="AY226" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ226" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA226" t="n">
         <v>4</v>
@@ -49967,19 +49967,19 @@
         <v>0.95</v>
       </c>
       <c r="AR227" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AS227" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AT227" t="n">
-        <v>3.78</v>
+        <v>3.51</v>
       </c>
       <c r="AU227" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV227" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW227" t="n">
         <v>5</v>
@@ -49988,10 +49988,10 @@
         <v>9</v>
       </c>
       <c r="AY227" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ227" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA227" t="n">
         <v>3</v>
@@ -50185,19 +50185,19 @@
         <v>1.05</v>
       </c>
       <c r="AR228" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS228" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT228" t="n">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="AU228" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW228" t="n">
         <v>16</v>
@@ -50206,10 +50206,10 @@
         <v>11</v>
       </c>
       <c r="AY228" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ228" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA228" t="n">
         <v>5</v>
@@ -50403,19 +50403,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS229" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT229" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="AU229" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV229" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW229" t="n">
         <v>12</v>
@@ -50424,10 +50424,10 @@
         <v>6</v>
       </c>
       <c r="AY229" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ229" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA229" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20242025.xlsx
@@ -49322,22 +49322,22 @@
         <v>2.47</v>
       </c>
       <c r="AU224" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW224" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX224" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ224" t="n">
         <v>8</v>
-      </c>
-      <c r="AY224" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ224" t="n">
-        <v>10</v>
       </c>
       <c r="BA224" t="n">
         <v>10</v>
@@ -49540,22 +49540,22 @@
         <v>2.62</v>
       </c>
       <c r="AU225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV225" t="n">
         <v>1</v>
       </c>
       <c r="AW225" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AX225" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ225" t="n">
         <v>6</v>
-      </c>
-      <c r="AY225" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ225" t="n">
-        <v>7</v>
       </c>
       <c r="BA225" t="n">
         <v>10</v>
@@ -49758,22 +49758,22 @@
         <v>2.75</v>
       </c>
       <c r="AU226" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV226" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AW226" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX226" t="n">
         <v>4</v>
       </c>
       <c r="AY226" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ226" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA226" t="n">
         <v>4</v>
@@ -49976,22 +49976,22 @@
         <v>3.51</v>
       </c>
       <c r="AU227" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV227" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW227" t="n">
         <v>5</v>
       </c>
       <c r="AX227" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY227" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ227" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA227" t="n">
         <v>3</v>
@@ -50200,16 +50200,16 @@
         <v>1</v>
       </c>
       <c r="AW228" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AX228" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AY228" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ228" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA228" t="n">
         <v>5</v>
@@ -50412,19 +50412,19 @@
         <v>3.29</v>
       </c>
       <c r="AU229" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV229" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX229" t="n">
         <v>5</v>
       </c>
-      <c r="AW229" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX229" t="n">
-        <v>6</v>
-      </c>
       <c r="AY229" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ229" t="n">
         <v>11</v>
